--- a/education_forms/014_ai_ethics_in_education_research_application_form--education_forms.xlsx
+++ b/education_forms/014_ai_ethics_in_education_research_application_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'data_privacy_and_protection',_'value':_'privacy'}</t>
+          <t>data_privacy_and_protection</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Data Privacy and Protection', 'value': 'privacy'}</t>
+          <t>Data Privacy and Protection</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'algorithmic_bias_and_fairness',_'value':_'bias_fairness'}</t>
+          <t>algorithmic_bias_and_fairness</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Algorithmic Bias and Fairness', 'value': 'bias_fairness'}</t>
+          <t>Algorithmic Bias and Fairness</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'human_agency_and_oversight',_'value':_'human_agency'}</t>
+          <t>human_agency_and_oversight</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Human Agency and Oversight', 'value': 'human_agency'}</t>
+          <t>Human Agency and Oversight</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'transparency_and_explainability',_'value':_'transparency'}</t>
+          <t>transparency_and_explainability</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Transparency and Explainability', 'value': 'transparency'}</t>
+          <t>Transparency and Explainability</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'safety_and_robustness',_'value':_'safety'}</t>
+          <t>safety_and_robustness</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Safety and Robustness', 'value': 'safety'}</t>
+          <t>Safety and Robustness</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'accountability',_'value':_'accountability'}</t>
+          <t>accountability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Accountability', 'value': 'accountability'}</t>
+          <t>Accountability</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'low_(minimal_risk_to_participants)',_'value':_'low'}</t>
+          <t>low_(minimal_risk_to_participants)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Low (Minimal risk to participants)', 'value': 'low'}</t>
+          <t>Low (Minimal risk to participants)</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'medium_(some_potential_for_bias_or_data_exposure)',_'value':_'medium'}</t>
+          <t>medium_(some_potential_for_bias_or_data_exposure)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Medium (Some potential for bias or data exposure)', 'value': 'medium'}</t>
+          <t>Medium (Some potential for bias or data exposure)</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'high_(involves_sensitive_data_or_significant_impact_on_learners)',_'value':_'high'}</t>
+          <t>high_(involves_sensitive_data_or_significant_impact_on_learners)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'High (Involves sensitive data or significant impact on learners)', 'value': 'high'}</t>
+          <t>High (Involves sensitive data or significant impact on learners)</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_agree',_'value':_true}</t>
+          <t>yes,_i_agree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I agree', 'value': True}</t>
+          <t>Yes, I agree</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_approved',_'value':_'approved'}</t>
+          <t>yes,_approved</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, approved', 'value': 'approved'}</t>
+          <t>Yes, approved</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'under_review',_'value':_'review'}</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Under review', 'value': 'review'}</t>
+          <t>Under review</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'not_yet_reviewed',_'value':_'pending'}</t>
+          <t>not_yet_reviewed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Not yet reviewed', 'value': 'pending'}</t>
+          <t>Not yet reviewed</t>
         </is>
       </c>
     </row>
